--- a/jewellery_catalog.xlsx
+++ b/jewellery_catalog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="105">
   <si>
     <t>code</t>
   </si>
@@ -102,6 +102,18 @@
     <t>For the special one</t>
   </si>
   <si>
+    <t>images/ring-11.JPG</t>
+  </si>
+  <si>
+    <t>images/ring-22.JPG</t>
+  </si>
+  <si>
+    <t>images/ring-33.JPG</t>
+  </si>
+  <si>
+    <t>images/ring-44.JPG</t>
+  </si>
+  <si>
     <t>Star Moon Bracelet</t>
   </si>
   <si>
@@ -114,6 +126,21 @@
     <t>Close ones Bracelet</t>
   </si>
   <si>
+    <t>images/bracelet-1.JPG</t>
+  </si>
+  <si>
+    <t>images/bracelet-2.JPG</t>
+  </si>
+  <si>
+    <t>images/bracelet-3.JPG</t>
+  </si>
+  <si>
+    <t>images/bracelet-4.JPG</t>
+  </si>
+  <si>
+    <t>images/bracelet-5.JPG</t>
+  </si>
+  <si>
     <t>BR001</t>
   </si>
   <si>
@@ -234,31 +261,76 @@
     <t>Modern trend Earring</t>
   </si>
   <si>
-    <t>images/bracelet-1.jpg</t>
-  </si>
-  <si>
-    <t>images/bracelet-2.jpg</t>
-  </si>
-  <si>
-    <t>images/bracelet-3.jpg</t>
-  </si>
-  <si>
-    <t>images/bracelet-4.jpg</t>
-  </si>
-  <si>
-    <t>images/bracelet-5.jpg</t>
-  </si>
-  <si>
-    <t>images/ring-11.jpg</t>
-  </si>
-  <si>
-    <t>images/ring-22.jpg</t>
-  </si>
-  <si>
-    <t>images/ring-33.jpg</t>
-  </si>
-  <si>
-    <t>images/ring-44.jpg</t>
+    <t>description</t>
+  </si>
+  <si>
+    <t>A beautifully crafted floral ring in 22 ct gold (916 hallmark) that adds grace to your everyday look. Its delicate design reflects elegance and charm. Perfect for gifting or personal styling.</t>
+  </si>
+  <si>
+    <t>Inspired by nature, this 22 ct 916 hallmark gold ring features a stylish leaf pattern. Lightweight yet eye-catching, it’s ideal for daily wear. A subtle blend of simplicity and beauty.</t>
+  </si>
+  <si>
+    <t>This 22 ct gold ring (916 hallmark) is designed to capture seasonal elegance with a modern twist. Its bold yet refined look makes it stand out effortlessly. Great for special occasions.</t>
+  </si>
+  <si>
+    <t>A meaningful 22 ct 916 hallmark gold ring crafted for someone truly special. Its elegant finish makes it perfect for gifting moments. A timeless piece that expresses love and appreciation.</t>
+  </si>
+  <si>
+    <t>A sleek and stylish bracelet made from 22 ct 916 hallmark gold. Its minimal design makes it perfect for both daily wear and occasions. Adds a touch of sophistication to any outfit.</t>
+  </si>
+  <si>
+    <t>Featuring a celestial-inspired design, this 22 ct gold bracelet (916 hallmark) shines with elegance. A trendy choice for modern wearers. Perfect for adding a unique charm to your look.</t>
+  </si>
+  <si>
+    <t>Crafted with love, this 22 ct 916 hallmark gold bracelet features a delicate heart design. Lightweight and meaningful, it’s ideal for everyday wear. A perfect symbol of affection.</t>
+  </si>
+  <si>
+    <t>Simple, durable, and elegant — this 22 ct gold bracelet (916 hallmark) is made for daily comfort. Its clean design pairs well with any outfit. A must-have everyday accessory.</t>
+  </si>
+  <si>
+    <t>A thoughtful 22 ct 916 hallmark gold bracelet designed to celebrate bonds. Its elegant finish makes it perfect for gifting loved ones. Stylish and sentimental.</t>
+  </si>
+  <si>
+    <t>A timeless 22 ct 916 hallmark gold chain with a bold and classic look. Ideal for both men and women. Perfect for regular wear or layering.</t>
+  </si>
+  <si>
+    <t>This 22 ct gold chain (916 hallmark) is designed for stone pendants or elegant styling. Its sturdy build ensures durability with style. A great choice for festive occasions.</t>
+  </si>
+  <si>
+    <t>Precision-crafted 22 ct 916 hallmark gold chain with a smooth and uniform finish. Strong, reliable, and perfect for daily wear. Combines durability with elegance.</t>
+  </si>
+  <si>
+    <t>A stylish 22 ct gold chain (916 hallmark) with a slightly heavier and premium feel. Designed for those who prefer bold yet simple designs. Perfect for statement wear.</t>
+  </si>
+  <si>
+    <t>Specially designed 22 ct 916 hallmark gold chain ideal for pendants. Its balanced design enhances the beauty of any pendant. Elegant and versatile.</t>
+  </si>
+  <si>
+    <t>A lighter version of the classic chain in 22 ct gold (916 hallmark). Comfortable for all-day wear without compromising on style. Perfect for everyday elegance.</t>
+  </si>
+  <si>
+    <t>Nature-inspired 22 ct 916 hallmark gold earrings with a delicate leaf design. Lightweight and elegant for daily wear. Adds a subtle charm to your look.</t>
+  </si>
+  <si>
+    <t>Beautifully crafted 22 ct gold (916 hallmark) earrings featuring a heart motif. Perfect for expressing love and style. Suitable for both casual and special occasions.</t>
+  </si>
+  <si>
+    <t>A simple yet classy pair of 22 ct 916 hallmark gold earrings. Designed for effortless elegance. Ideal for daily wear or office use.</t>
+  </si>
+  <si>
+    <t>Comfortable and stylish 22 ct gold earrings (916 hallmark) made for everyday wear. Lightweight and durable. A perfect addition to your daily accessories.</t>
+  </si>
+  <si>
+    <t>Symbolizing connection, these 22 ct 916 hallmark gold earrings are simple yet meaningful. Great for gifting and daily styling. Elegant and versatile.</t>
+  </si>
+  <si>
+    <t>A stylish pair of 22 ct gold (916 hallmark) earrings representing togetherness. Modern design with a touch of elegance. Perfect for casual and festive wear.</t>
+  </si>
+  <si>
+    <t>Ultra-light 22 ct 916 hallmark gold earrings designed for all-day comfort. Simple, elegant, and easy to carry. Ideal for daily use.</t>
+  </si>
+  <si>
+    <t>A trendy 22 ct gold (916 hallmark) earring design for modern fashion lovers. Stylish and eye-catching. Perfect for making a statement.</t>
   </si>
 </sst>
 </file>
@@ -326,7 +398,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -337,6 +409,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -639,20 +712,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="43.5703125" customWidth="1"/>
-    <col min="7" max="7" width="37.140625" customWidth="1"/>
-    <col min="8" max="8" width="56.5703125" customWidth="1"/>
+    <col min="2" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="43.5703125" customWidth="1"/>
+    <col min="8" max="8" width="37.140625" customWidth="1"/>
+    <col min="9" max="9" width="56.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,620 +733,692 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>2500</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>2500</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>6.1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>2500</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>7.1</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>2500</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>2.5</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>2000</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="F7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="E8" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="2">
         <v>2000</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="G8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="E9" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F9" s="2">
         <v>2000</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="G9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="2">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="E10" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="F10" s="2">
         <v>2000</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2000</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>12.5</v>
       </c>
-      <c r="E11" s="2">
+      <c r="F11" s="2">
         <v>8000</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E12" s="2">
+      <c r="F12" s="2">
         <v>7000</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>7.3</v>
       </c>
-      <c r="E13" s="2">
+      <c r="F13" s="2">
         <v>6000</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>11.2</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F14" s="2">
         <v>10300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="G14" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>7.5</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
         <v>8000</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>8.6</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F16" s="2">
         <v>9500</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="G16" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2100</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3200</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1800</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="2">
-        <v>2.1</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2100</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="B20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2800</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="2">
-        <v>3.2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>3200</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="B21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1800</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="2">
-        <v>2.9</v>
-      </c>
-      <c r="E20" s="2">
-        <v>2800</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="E21" s="2">
-        <v>2000</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="2">
+        <v>67</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="2">
         <v>2.6</v>
       </c>
-      <c r="E22" s="2">
+      <c r="F22" s="2">
         <v>2500</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="2">
+      <c r="E23" s="2">
         <v>1.75</v>
       </c>
-      <c r="E23" s="2">
+      <c r="F23" s="2">
         <v>1700</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="2">
+        <v>80</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="2">
         <v>2.56</v>
       </c>
-      <c r="E24" s="2">
+      <c r="F24" s="2">
         <v>2500</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="G24" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/jewellery_catalog.xlsx
+++ b/jewellery_catalog.xlsx
@@ -102,18 +102,6 @@
     <t>For the special one</t>
   </si>
   <si>
-    <t>images/ring-11.JPG</t>
-  </si>
-  <si>
-    <t>images/ring-22.JPG</t>
-  </si>
-  <si>
-    <t>images/ring-33.JPG</t>
-  </si>
-  <si>
-    <t>images/ring-44.JPG</t>
-  </si>
-  <si>
     <t>Star Moon Bracelet</t>
   </si>
   <si>
@@ -126,21 +114,6 @@
     <t>Close ones Bracelet</t>
   </si>
   <si>
-    <t>images/bracelet-1.JPG</t>
-  </si>
-  <si>
-    <t>images/bracelet-2.JPG</t>
-  </si>
-  <si>
-    <t>images/bracelet-3.JPG</t>
-  </si>
-  <si>
-    <t>images/bracelet-4.JPG</t>
-  </si>
-  <si>
-    <t>images/bracelet-5.JPG</t>
-  </si>
-  <si>
     <t>BR001</t>
   </si>
   <si>
@@ -331,6 +304,33 @@
   </si>
   <si>
     <t>A trendy 22 ct gold (916 hallmark) earring design for modern fashion lovers. Stylish and eye-catching. Perfect for making a statement.</t>
+  </si>
+  <si>
+    <t>images/ring-11.jpg</t>
+  </si>
+  <si>
+    <t>images/ring-22.jpg</t>
+  </si>
+  <si>
+    <t>images/ring-33.jpg</t>
+  </si>
+  <si>
+    <t>images/ring-44.jpg</t>
+  </si>
+  <si>
+    <t>images/bracelet-1.jpg</t>
+  </si>
+  <si>
+    <t>images/bracelet-2.jpg</t>
+  </si>
+  <si>
+    <t>images/bracelet-3.jpg</t>
+  </si>
+  <si>
+    <t>images/bracelet-4.jpg</t>
+  </si>
+  <si>
+    <t>images/bracelet-5.jpg</t>
   </si>
 </sst>
 </file>
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -762,7 +762,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -774,13 +774,13 @@
         <v>2500</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -791,7 +791,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -803,13 +803,13 @@
         <v>2500</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -820,7 +820,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -832,13 +832,13 @@
         <v>2500</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -849,7 +849,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -861,24 +861,24 @@
         <v>2500</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>16</v>
@@ -890,24 +890,24 @@
         <v>2000</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>16</v>
@@ -919,24 +919,24 @@
         <v>2000</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>16</v>
@@ -948,24 +948,24 @@
         <v>2000</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>16</v>
@@ -977,24 +977,24 @@
         <v>2000</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>16</v>
@@ -1006,13 +1006,13 @@
         <v>2000</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1023,7 +1023,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -1035,13 +1035,13 @@
         <v>8000</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1052,7 +1052,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -1064,13 +1064,13 @@
         <v>7000</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1081,7 +1081,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -1093,13 +1093,13 @@
         <v>6000</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1110,7 +1110,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -1122,24 +1122,24 @@
         <v>10300</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -1151,24 +1151,24 @@
         <v>8000</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -1180,27 +1180,27 @@
         <v>9500</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2">
         <v>2.1</v>
@@ -1209,27 +1209,27 @@
         <v>2100</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E18" s="2">
         <v>3.2</v>
@@ -1238,27 +1238,27 @@
         <v>3200</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E19" s="2">
         <v>1.8</v>
@@ -1267,27 +1267,27 @@
         <v>1800</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E20" s="2">
         <v>2.9</v>
@@ -1296,27 +1296,27 @@
         <v>2800</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E21" s="2">
         <v>1.5</v>
@@ -1325,27 +1325,27 @@
         <v>2000</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E22" s="2">
         <v>2.6</v>
@@ -1354,27 +1354,27 @@
         <v>2500</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2">
         <v>1.75</v>
@@ -1383,27 +1383,27 @@
         <v>1700</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2">
         <v>2.56</v>
@@ -1412,13 +1412,13 @@
         <v>2500</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
